--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-evenement.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-evenement.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7278" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7278" uniqueCount="550">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -783,6 +783,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Encounter.code.qualifier</t>
@@ -7392,7 +7396,7 @@
         <v>74</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>74</v>
@@ -7400,17 +7404,17 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>80</v>
@@ -7428,13 +7432,13 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7485,7 +7489,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7505,10 +7509,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7606,17 +7610,17 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>80</v>
@@ -7634,11 +7638,11 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7689,7 +7693,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7709,10 +7713,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7737,13 +7741,13 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7794,7 +7798,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7814,10 +7818,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7845,10 +7849,10 @@
         <v>171</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7899,7 +7903,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7919,17 +7923,17 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>80</v>
@@ -7951,7 +7955,7 @@
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8002,7 +8006,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8022,10 +8026,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8051,7 +8055,7 @@
         <v>205</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -8103,7 +8107,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8123,10 +8127,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8224,10 +8228,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8325,10 +8329,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8428,10 +8432,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8529,10 +8533,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8632,10 +8636,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8733,10 +8737,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8830,10 +8834,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8935,10 +8939,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9038,10 +9042,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9133,7 +9137,7 @@
         <v>74</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>74</v>
@@ -9141,10 +9145,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9170,10 +9174,10 @@
         <v>91</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9204,7 +9208,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -9222,7 +9226,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -9242,10 +9246,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9268,13 +9272,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9325,7 +9329,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -9345,10 +9349,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9371,7 +9375,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -9424,7 +9428,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -9444,10 +9448,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9470,7 +9474,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -9503,25 +9507,25 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9541,10 +9545,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9567,7 +9571,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -9620,7 +9624,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9640,10 +9644,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9666,7 +9670,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9719,7 +9723,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9739,10 +9743,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9765,10 +9769,10 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -9820,7 +9824,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9840,10 +9844,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9866,10 +9870,10 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -9921,7 +9925,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9941,10 +9945,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9967,10 +9971,10 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -10022,7 +10026,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -10042,10 +10046,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10068,10 +10072,10 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -10123,7 +10127,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -10143,10 +10147,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10169,7 +10173,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -10210,7 +10214,7 @@
         <v>74</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AC80" s="2"/>
       <c r="AD80" t="s" s="2">
@@ -10220,7 +10224,7 @@
         <v>124</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -10240,13 +10244,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>74</v>
@@ -10268,10 +10272,10 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -10323,7 +10327,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -10343,10 +10347,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10444,10 +10448,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10545,10 +10549,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10646,10 +10650,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10747,10 +10751,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10850,10 +10854,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10953,10 +10957,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11056,10 +11060,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11159,10 +11163,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11260,10 +11264,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11300,7 +11304,7 @@
         <v>74</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>74</v>
@@ -11319,7 +11323,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>74</v>
@@ -11337,7 +11341,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
@@ -11357,10 +11361,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11387,7 +11391,7 @@
       </c>
       <c r="L92" s="2"/>
       <c r="M92" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11438,7 +11442,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -11458,10 +11462,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11488,12 +11492,12 @@
       </c>
       <c r="L93" s="2"/>
       <c r="M93" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
@@ -11539,7 +11543,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11559,10 +11563,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11638,7 +11642,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11658,10 +11662,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11684,7 +11688,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11737,7 +11741,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11757,10 +11761,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11783,7 +11787,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11836,7 +11840,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11856,10 +11860,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11882,7 +11886,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11935,7 +11939,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11955,10 +11959,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11981,7 +11985,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -12034,7 +12038,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -12054,10 +12058,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12080,7 +12084,7 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -12133,7 +12137,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -12153,10 +12157,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12179,7 +12183,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -12232,7 +12236,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -12252,10 +12256,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12278,7 +12282,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -12331,7 +12335,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -12351,10 +12355,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12377,7 +12381,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -12430,7 +12434,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -12450,10 +12454,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12476,7 +12480,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12529,7 +12533,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12549,10 +12553,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12575,7 +12579,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12628,7 +12632,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12648,10 +12652,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12674,7 +12678,7 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12727,7 +12731,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12747,13 +12751,13 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>74</v>
@@ -12775,10 +12779,10 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
@@ -12830,7 +12834,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12850,10 +12854,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12951,10 +12955,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13052,10 +13056,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13153,10 +13157,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13254,10 +13258,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13357,10 +13361,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13460,10 +13464,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13563,10 +13567,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13666,10 +13670,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13767,10 +13771,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13807,7 +13811,7 @@
         <v>74</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>74</v>
@@ -13826,7 +13830,7 @@
       </c>
       <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>74</v>
@@ -13844,7 +13848,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>75</v>
@@ -13864,10 +13868,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13894,7 +13898,7 @@
       </c>
       <c r="L117" s="2"/>
       <c r="M117" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -13906,7 +13910,7 @@
         <v>74</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>74</v>
@@ -13945,7 +13949,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13965,10 +13969,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13995,12 +13999,12 @@
       </c>
       <c r="L118" s="2"/>
       <c r="M118" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
@@ -14046,7 +14050,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -14066,10 +14070,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14145,7 +14149,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -14165,10 +14169,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14191,7 +14195,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -14244,7 +14248,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -14264,10 +14268,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14290,7 +14294,7 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -14343,7 +14347,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -14363,10 +14367,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14389,7 +14393,7 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -14442,7 +14446,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14462,10 +14466,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14488,7 +14492,7 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
@@ -14541,7 +14545,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14561,10 +14565,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14587,7 +14591,7 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -14640,7 +14644,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14660,10 +14664,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14686,7 +14690,7 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -14739,7 +14743,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14759,10 +14763,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14785,7 +14789,7 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -14838,7 +14842,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14858,10 +14862,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14884,7 +14888,7 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -14937,7 +14941,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14957,10 +14961,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14983,7 +14987,7 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -15036,7 +15040,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -15056,10 +15060,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15082,7 +15086,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -15135,7 +15139,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -15155,10 +15159,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15181,7 +15185,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -15234,7 +15238,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -15254,13 +15258,13 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>74</v>
@@ -15282,10 +15286,10 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
@@ -15337,7 +15341,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -15357,10 +15361,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15458,10 +15462,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15559,10 +15563,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15660,10 +15664,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15761,10 +15765,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15864,10 +15868,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15967,10 +15971,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16070,10 +16074,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16173,10 +16177,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16274,10 +16278,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16314,7 +16318,7 @@
         <v>74</v>
       </c>
       <c r="S141" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T141" t="s" s="2">
         <v>74</v>
@@ -16333,7 +16337,7 @@
       </c>
       <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>74</v>
@@ -16351,7 +16355,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>75</v>
@@ -16371,10 +16375,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16401,7 +16405,7 @@
       </c>
       <c r="L142" s="2"/>
       <c r="M142" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -16452,7 +16456,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -16472,10 +16476,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16502,12 +16506,12 @@
       </c>
       <c r="L143" s="2"/>
       <c r="M143" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q143" s="2"/>
       <c r="R143" t="s" s="2">
@@ -16553,7 +16557,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16573,10 +16577,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16652,7 +16656,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16672,10 +16676,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16698,7 +16702,7 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16751,7 +16755,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16771,10 +16775,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16797,7 +16801,7 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16850,7 +16854,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -16870,10 +16874,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16896,7 +16900,7 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
@@ -16949,7 +16953,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -16969,10 +16973,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16995,7 +16999,7 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
@@ -17048,7 +17052,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -17068,10 +17072,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17094,7 +17098,7 @@
         <v>74</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
@@ -17147,7 +17151,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -17167,10 +17171,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17193,7 +17197,7 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
@@ -17246,7 +17250,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -17266,10 +17270,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17292,7 +17296,7 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
@@ -17345,7 +17349,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -17365,10 +17369,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17391,7 +17395,7 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
@@ -17444,7 +17448,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17464,10 +17468,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17490,7 +17494,7 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
@@ -17543,7 +17547,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17563,10 +17567,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17589,7 +17593,7 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -17642,7 +17646,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -17662,10 +17666,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17688,7 +17692,7 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -17741,7 +17745,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -17761,13 +17765,13 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>74</v>
@@ -17789,10 +17793,10 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
@@ -17844,7 +17848,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -17864,10 +17868,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17965,10 +17969,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18066,10 +18070,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18167,10 +18171,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18268,10 +18272,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18371,10 +18375,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18474,10 +18478,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18577,10 +18581,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18680,10 +18684,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18781,10 +18785,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18821,7 +18825,7 @@
         <v>74</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>74</v>
@@ -18840,7 +18844,7 @@
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>74</v>
@@ -18858,7 +18862,7 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>75</v>
@@ -18878,10 +18882,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18908,7 +18912,7 @@
       </c>
       <c r="L167" s="2"/>
       <c r="M167" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -18959,7 +18963,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -18979,10 +18983,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19009,12 +19013,12 @@
       </c>
       <c r="L168" s="2"/>
       <c r="M168" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q168" s="2"/>
       <c r="R168" t="s" s="2">
@@ -19060,7 +19064,7 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -19080,10 +19084,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19159,7 +19163,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -19179,10 +19183,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19205,7 +19209,7 @@
         <v>74</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -19258,7 +19262,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -19278,10 +19282,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19304,7 +19308,7 @@
         <v>74</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -19357,7 +19361,7 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -19377,10 +19381,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19403,7 +19407,7 @@
         <v>74</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
@@ -19456,7 +19460,7 @@
         <v>74</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -19476,10 +19480,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19502,7 +19506,7 @@
         <v>74</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
@@ -19555,7 +19559,7 @@
         <v>74</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -19575,10 +19579,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19601,7 +19605,7 @@
         <v>74</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -19654,7 +19658,7 @@
         <v>74</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -19674,10 +19678,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19700,7 +19704,7 @@
         <v>74</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
@@ -19753,7 +19757,7 @@
         <v>74</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -19773,10 +19777,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19799,7 +19803,7 @@
         <v>74</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
@@ -19852,7 +19856,7 @@
         <v>74</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -19872,10 +19876,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -19898,7 +19902,7 @@
         <v>74</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
@@ -19951,7 +19955,7 @@
         <v>74</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -19971,10 +19975,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -19997,7 +20001,7 @@
         <v>74</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
@@ -20050,7 +20054,7 @@
         <v>74</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -20070,10 +20074,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20096,7 +20100,7 @@
         <v>74</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
@@ -20149,7 +20153,7 @@
         <v>74</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -20169,10 +20173,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20195,7 +20199,7 @@
         <v>74</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
@@ -20248,7 +20252,7 @@
         <v>74</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -20268,13 +20272,13 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D181" t="s" s="2">
         <v>74</v>
@@ -20296,10 +20300,10 @@
         <v>74</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
@@ -20351,7 +20355,7 @@
         <v>74</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -20371,10 +20375,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20472,10 +20476,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20573,10 +20577,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20674,10 +20678,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20775,10 +20779,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20878,10 +20882,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -20981,10 +20985,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21084,10 +21088,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21187,10 +21191,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21288,10 +21292,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21328,7 +21332,7 @@
         <v>74</v>
       </c>
       <c r="S191" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T191" t="s" s="2">
         <v>74</v>
@@ -21347,7 +21351,7 @@
       </c>
       <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>74</v>
@@ -21365,7 +21369,7 @@
         <v>74</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>75</v>
@@ -21385,10 +21389,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21415,7 +21419,7 @@
       </c>
       <c r="L192" s="2"/>
       <c r="M192" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -21466,7 +21470,7 @@
         <v>74</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -21486,10 +21490,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21516,12 +21520,12 @@
       </c>
       <c r="L193" s="2"/>
       <c r="M193" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q193" s="2"/>
       <c r="R193" t="s" s="2">
@@ -21567,7 +21571,7 @@
         <v>74</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -21587,10 +21591,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21666,7 +21670,7 @@
         <v>74</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -21686,10 +21690,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -21712,7 +21716,7 @@
         <v>74</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
@@ -21765,7 +21769,7 @@
         <v>74</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -21785,10 +21789,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -21811,7 +21815,7 @@
         <v>74</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
@@ -21864,7 +21868,7 @@
         <v>74</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -21884,10 +21888,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -21910,7 +21914,7 @@
         <v>74</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
@@ -21963,7 +21967,7 @@
         <v>74</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -21983,10 +21987,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22009,7 +22013,7 @@
         <v>74</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
@@ -22062,7 +22066,7 @@
         <v>74</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -22082,10 +22086,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22108,7 +22112,7 @@
         <v>74</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
@@ -22161,7 +22165,7 @@
         <v>74</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -22181,10 +22185,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22207,7 +22211,7 @@
         <v>74</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
@@ -22260,7 +22264,7 @@
         <v>74</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -22280,10 +22284,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22306,7 +22310,7 @@
         <v>74</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
@@ -22359,7 +22363,7 @@
         <v>74</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -22379,10 +22383,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22405,7 +22409,7 @@
         <v>74</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
@@ -22458,7 +22462,7 @@
         <v>74</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -22478,10 +22482,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22504,7 +22508,7 @@
         <v>74</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
@@ -22557,7 +22561,7 @@
         <v>74</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -22577,10 +22581,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22603,7 +22607,7 @@
         <v>74</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
@@ -22656,7 +22660,7 @@
         <v>74</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -22676,10 +22680,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -22702,7 +22706,7 @@
         <v>74</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
@@ -22755,7 +22759,7 @@
         <v>74</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
@@ -22775,13 +22779,13 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D206" t="s" s="2">
         <v>74</v>
@@ -22803,10 +22807,10 @@
         <v>74</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M206" s="2"/>
       <c r="N206" s="2"/>
@@ -22858,7 +22862,7 @@
         <v>74</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
@@ -22878,10 +22882,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -22979,10 +22983,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23080,10 +23084,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23181,10 +23185,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23282,10 +23286,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23385,10 +23389,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23488,10 +23492,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23591,10 +23595,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23694,10 +23698,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -23795,10 +23799,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -23835,7 +23839,7 @@
         <v>74</v>
       </c>
       <c r="S216" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T216" t="s" s="2">
         <v>74</v>
@@ -23854,7 +23858,7 @@
       </c>
       <c r="Y216" s="2"/>
       <c r="Z216" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>74</v>
@@ -23872,7 +23876,7 @@
         <v>74</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>75</v>
@@ -23892,10 +23896,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -23922,7 +23926,7 @@
       </c>
       <c r="L217" s="2"/>
       <c r="M217" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -23973,7 +23977,7 @@
         <v>74</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>
@@ -23993,10 +23997,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24023,12 +24027,12 @@
       </c>
       <c r="L218" s="2"/>
       <c r="M218" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q218" s="2"/>
       <c r="R218" t="s" s="2">
@@ -24074,7 +24078,7 @@
         <v>74</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>80</v>
@@ -24094,10 +24098,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24173,7 +24177,7 @@
         <v>74</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>80</v>
@@ -24193,10 +24197,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24219,7 +24223,7 @@
         <v>74</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
@@ -24272,7 +24276,7 @@
         <v>74</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>80</v>
@@ -24292,10 +24296,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24318,7 +24322,7 @@
         <v>74</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
@@ -24371,7 +24375,7 @@
         <v>74</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>80</v>
@@ -24391,10 +24395,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24417,7 +24421,7 @@
         <v>74</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
@@ -24470,7 +24474,7 @@
         <v>74</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>80</v>
@@ -24490,10 +24494,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24516,7 +24520,7 @@
         <v>74</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -24569,7 +24573,7 @@
         <v>74</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>80</v>
@@ -24589,10 +24593,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -24615,7 +24619,7 @@
         <v>74</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
@@ -24668,7 +24672,7 @@
         <v>74</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
@@ -24688,10 +24692,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -24714,7 +24718,7 @@
         <v>74</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L225" s="2"/>
       <c r="M225" s="2"/>
@@ -24767,7 +24771,7 @@
         <v>74</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -24787,10 +24791,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -24813,7 +24817,7 @@
         <v>74</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L226" s="2"/>
       <c r="M226" s="2"/>
@@ -24866,7 +24870,7 @@
         <v>74</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>80</v>
@@ -24886,10 +24890,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -24912,7 +24916,7 @@
         <v>74</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
@@ -24965,7 +24969,7 @@
         <v>74</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>80</v>
@@ -24985,10 +24989,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25011,7 +25015,7 @@
         <v>74</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L228" s="2"/>
       <c r="M228" s="2"/>
@@ -25064,7 +25068,7 @@
         <v>74</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>80</v>
@@ -25084,10 +25088,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -25110,7 +25114,7 @@
         <v>74</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
@@ -25163,7 +25167,7 @@
         <v>74</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>80</v>
@@ -25183,10 +25187,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -25209,7 +25213,7 @@
         <v>74</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L230" s="2"/>
       <c r="M230" s="2"/>
@@ -25262,7 +25266,7 @@
         <v>74</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>80</v>
@@ -25282,10 +25286,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25308,7 +25312,7 @@
         <v>74</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L231" s="2"/>
       <c r="M231" s="2"/>
@@ -25361,7 +25365,7 @@
         <v>74</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>80</v>
@@ -25381,10 +25385,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -25407,7 +25411,7 @@
         <v>74</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L232" s="2"/>
       <c r="M232" s="2"/>
@@ -25460,7 +25464,7 @@
         <v>74</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>80</v>
@@ -25480,10 +25484,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -25506,7 +25510,7 @@
         <v>74</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L233" s="2"/>
       <c r="M233" s="2"/>
@@ -25559,7 +25563,7 @@
         <v>74</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>80</v>
@@ -25579,10 +25583,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -25605,7 +25609,7 @@
         <v>74</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L234" s="2"/>
       <c r="M234" s="2"/>
@@ -25658,7 +25662,7 @@
         <v>74</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>80</v>
